--- a/output/yearly_population_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_42_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5912</v>
+        <v>4670</v>
       </c>
       <c r="C2" t="n">
-        <v>8532</v>
+        <v>7193</v>
       </c>
       <c r="D2" t="n">
-        <v>14614</v>
+        <v>37189</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3549</v>
+        <v>2866</v>
       </c>
       <c r="C3" t="n">
-        <v>2415</v>
+        <v>6565</v>
       </c>
       <c r="D3" t="n">
-        <v>10741</v>
+        <v>16964</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2945</v>
+        <v>2417</v>
       </c>
       <c r="C4" t="n">
-        <v>3717</v>
+        <v>7261</v>
       </c>
       <c r="D4" t="n">
-        <v>5530</v>
+        <v>8673</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1907</v>
+        <v>1672</v>
       </c>
       <c r="C5" t="n">
-        <v>4346</v>
+        <v>5921</v>
       </c>
       <c r="D5" t="n">
-        <v>2252</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1092</v>
+        <v>946</v>
       </c>
       <c r="C6" t="n">
-        <v>3648</v>
+        <v>3717</v>
       </c>
       <c r="D6" t="n">
-        <v>1048</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>535</v>
+        <v>435</v>
       </c>
       <c r="C7" t="n">
-        <v>2313</v>
+        <v>2181</v>
       </c>
       <c r="D7" t="n">
-        <v>640</v>
+        <v>654</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>161</v>
       </c>
       <c r="C8" t="n">
-        <v>1163</v>
+        <v>1072</v>
       </c>
       <c r="D8" t="n">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C9" t="n">
-        <v>469</v>
+        <v>422</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7987</v>
+        <v>5298</v>
       </c>
       <c r="C2" t="n">
-        <v>6292</v>
+        <v>5903</v>
       </c>
       <c r="D2" t="n">
-        <v>19336</v>
+        <v>32700</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3740</v>
+        <v>2946</v>
       </c>
       <c r="C3" t="n">
-        <v>4572</v>
+        <v>6044</v>
       </c>
       <c r="D3" t="n">
-        <v>10545</v>
+        <v>18439</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2775</v>
+        <v>2229</v>
       </c>
       <c r="C4" t="n">
-        <v>3014</v>
+        <v>6726</v>
       </c>
       <c r="D4" t="n">
-        <v>6212</v>
+        <v>9682</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2078</v>
+        <v>1755</v>
       </c>
       <c r="C5" t="n">
-        <v>3924</v>
+        <v>6389</v>
       </c>
       <c r="D5" t="n">
-        <v>2665</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1312</v>
+        <v>1139</v>
       </c>
       <c r="C6" t="n">
-        <v>3891</v>
+        <v>4577</v>
       </c>
       <c r="D6" t="n">
-        <v>1218</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>699</v>
+        <v>571</v>
       </c>
       <c r="C7" t="n">
-        <v>2913</v>
+        <v>2827</v>
       </c>
       <c r="D7" t="n">
-        <v>687</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>295</v>
+        <v>236</v>
       </c>
       <c r="C8" t="n">
-        <v>1647</v>
+        <v>1506</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="C9" t="n">
-        <v>761</v>
+        <v>672</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" t="n">
-        <v>321</v>
+        <v>297</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,10 +1220,10 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1237,7 +1237,7 @@
         <v>138</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8094</v>
+        <v>6464</v>
       </c>
       <c r="C2" t="n">
-        <v>14519</v>
+        <v>10903</v>
       </c>
       <c r="D2" t="n">
-        <v>23505</v>
+        <v>31131</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4403</v>
+        <v>3157</v>
       </c>
       <c r="C3" t="n">
-        <v>4685</v>
+        <v>5337</v>
       </c>
       <c r="D3" t="n">
-        <v>10978</v>
+        <v>19147</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2700</v>
+        <v>2131</v>
       </c>
       <c r="C4" t="n">
-        <v>3610</v>
+        <v>6304</v>
       </c>
       <c r="D4" t="n">
-        <v>6688</v>
+        <v>10471</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2103</v>
+        <v>1732</v>
       </c>
       <c r="C5" t="n">
-        <v>3449</v>
+        <v>6327</v>
       </c>
       <c r="D5" t="n">
-        <v>3069</v>
+        <v>4415</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1479</v>
+        <v>1250</v>
       </c>
       <c r="C6" t="n">
-        <v>3831</v>
+        <v>5189</v>
       </c>
       <c r="D6" t="n">
-        <v>1410</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>857</v>
+        <v>700</v>
       </c>
       <c r="C7" t="n">
-        <v>3314</v>
+        <v>3494</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="C8" t="n">
-        <v>2126</v>
+        <v>1969</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C9" t="n">
-        <v>1091</v>
+        <v>959</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>484</v>
+        <v>422</v>
       </c>
       <c r="D10" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>233</v>
+        <v>220</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7423</v>
+        <v>5930</v>
       </c>
       <c r="C2" t="n">
-        <v>9872</v>
+        <v>7675</v>
       </c>
       <c r="D2" t="n">
-        <v>19225</v>
+        <v>25823</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5113</v>
+        <v>3752</v>
       </c>
       <c r="C3" t="n">
-        <v>7695</v>
+        <v>8893</v>
       </c>
       <c r="D3" t="n">
-        <v>12107</v>
+        <v>20779</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1943</v>
+        <v>1600</v>
       </c>
       <c r="C4" t="n">
-        <v>5321</v>
+        <v>9402</v>
       </c>
       <c r="D4" t="n">
-        <v>6551</v>
+        <v>9828</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1366</v>
+        <v>1155</v>
       </c>
       <c r="C5" t="n">
-        <v>3754</v>
+        <v>5085</v>
       </c>
       <c r="D5" t="n">
-        <v>2206</v>
+        <v>2836</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>791</v>
+        <v>646</v>
       </c>
       <c r="C6" t="n">
-        <v>3247</v>
+        <v>3424</v>
       </c>
       <c r="D6" t="n">
-        <v>731</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>291</v>
       </c>
       <c r="C7" t="n">
-        <v>2083</v>
+        <v>1929</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>1069</v>
+        <v>939</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>474</v>
+        <v>413</v>
       </c>
       <c r="D9" t="n">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
         <v>199</v>
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4428</v>
+        <v>3560</v>
       </c>
       <c r="C2" t="n">
-        <v>4087</v>
+        <v>3418</v>
       </c>
       <c r="D2" t="n">
-        <v>13339</v>
+        <v>18770</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5266</v>
+        <v>4023</v>
       </c>
       <c r="C3" t="n">
-        <v>7874</v>
+        <v>7618</v>
       </c>
       <c r="D3" t="n">
-        <v>12377</v>
+        <v>20261</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2766</v>
+        <v>2072</v>
       </c>
       <c r="C4" t="n">
-        <v>6531</v>
+        <v>9252</v>
       </c>
       <c r="D4" t="n">
-        <v>7331</v>
+        <v>11294</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1499</v>
+        <v>1252</v>
       </c>
       <c r="C5" t="n">
-        <v>4502</v>
+        <v>6922</v>
       </c>
       <c r="D5" t="n">
-        <v>2723</v>
+        <v>3609</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>944</v>
+        <v>759</v>
       </c>
       <c r="C6" t="n">
-        <v>3588</v>
+        <v>4142</v>
       </c>
       <c r="D6" t="n">
-        <v>885</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7">
@@ -2094,10 +2094,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>345</v>
+        <v>270</v>
       </c>
       <c r="C7" t="n">
-        <v>2585</v>
+        <v>2479</v>
       </c>
       <c r="D7" t="n">
         <v>510</v>
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>1385</v>
+        <v>1221</v>
       </c>
       <c r="D8" t="n">
-        <v>338</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>536</v>
+        <v>449</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4359</v>
+        <v>3331</v>
       </c>
       <c r="C2" t="n">
-        <v>9412</v>
+        <v>5311</v>
       </c>
       <c r="D2" t="n">
-        <v>10719</v>
+        <v>17406</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4125</v>
+        <v>3224</v>
       </c>
       <c r="C3" t="n">
-        <v>5361</v>
+        <v>5096</v>
       </c>
       <c r="D3" t="n">
-        <v>11782</v>
+        <v>18891</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3321</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>7065</v>
+        <v>8290</v>
       </c>
       <c r="D4" t="n">
-        <v>7861</v>
+        <v>12219</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1805</v>
+        <v>1416</v>
       </c>
       <c r="C5" t="n">
-        <v>5425</v>
+        <v>7829</v>
       </c>
       <c r="D5" t="n">
-        <v>3392</v>
+        <v>4679</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1083</v>
+        <v>877</v>
       </c>
       <c r="C6" t="n">
-        <v>3965</v>
+        <v>5344</v>
       </c>
       <c r="D6" t="n">
-        <v>1155</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>514</v>
+        <v>399</v>
       </c>
       <c r="C7" t="n">
-        <v>3051</v>
+        <v>3186</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="C8" t="n">
-        <v>1891</v>
+        <v>1713</v>
       </c>
       <c r="D8" t="n">
-        <v>356</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>865</v>
+        <v>725</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>302</v>
       </c>
       <c r="D10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>35</v>
+      </c>
+      <c r="D16" t="n">
         <v>36</v>
-      </c>
-      <c r="D16" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2579</v>
+        <v>2017</v>
       </c>
       <c r="C2" t="n">
-        <v>4344</v>
+        <v>2612</v>
       </c>
       <c r="D2" t="n">
-        <v>7404</v>
+        <v>12156</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4068</v>
+        <v>3136</v>
       </c>
       <c r="C3" t="n">
-        <v>6582</v>
+        <v>5026</v>
       </c>
       <c r="D3" t="n">
-        <v>11380</v>
+        <v>18313</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3638</v>
+        <v>2732</v>
       </c>
       <c r="C4" t="n">
-        <v>7023</v>
+        <v>7932</v>
       </c>
       <c r="D4" t="n">
-        <v>8408</v>
+        <v>13100</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1901</v>
+        <v>1490</v>
       </c>
       <c r="C5" t="n">
-        <v>6649</v>
+        <v>9248</v>
       </c>
       <c r="D5" t="n">
-        <v>3650</v>
+        <v>4911</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>925</v>
+        <v>709</v>
       </c>
       <c r="C6" t="n">
-        <v>4930</v>
+        <v>6157</v>
       </c>
       <c r="D6" t="n">
-        <v>1140</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="C7" t="n">
-        <v>3323</v>
+        <v>3252</v>
       </c>
       <c r="D7" t="n">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C8" t="n">
-        <v>1440</v>
+        <v>1197</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>295</v>
       </c>
       <c r="D9" t="n">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>34</v>
+      </c>
+      <c r="D15" t="n">
         <v>35</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3917</v>
+        <v>2126</v>
       </c>
       <c r="C2" t="n">
-        <v>6295</v>
+        <v>5641</v>
       </c>
       <c r="D2" t="n">
-        <v>10778</v>
+        <v>10799</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2946</v>
+        <v>2285</v>
       </c>
       <c r="C3" t="n">
-        <v>4903</v>
+        <v>3560</v>
       </c>
       <c r="D3" t="n">
-        <v>10074</v>
+        <v>16323</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3339</v>
+        <v>2551</v>
       </c>
       <c r="C4" t="n">
-        <v>6728</v>
+        <v>6455</v>
       </c>
       <c r="D4" t="n">
-        <v>8637</v>
+        <v>13502</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2323</v>
+        <v>1755</v>
       </c>
       <c r="C5" t="n">
-        <v>6746</v>
+        <v>8575</v>
       </c>
       <c r="D5" t="n">
-        <v>4269</v>
+        <v>5940</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1195</v>
+        <v>904</v>
       </c>
       <c r="C6" t="n">
-        <v>5674</v>
+        <v>7409</v>
       </c>
       <c r="D6" t="n">
-        <v>1497</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>354</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>4048</v>
+        <v>4424</v>
       </c>
       <c r="D7" t="n">
-        <v>636</v>
+        <v>646</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>2168</v>
+        <v>1924</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>717</v>
+        <v>577</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>215</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>56</v>
+      </c>
+      <c r="D13" t="n">
         <v>60</v>
-      </c>
-      <c r="D13" t="n">
-        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
         <v>2</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2749</v>
+        <v>1458</v>
       </c>
       <c r="C2" t="n">
-        <v>3033</v>
+        <v>3442</v>
       </c>
       <c r="D2" t="n">
-        <v>8175</v>
+        <v>9356</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2859</v>
+        <v>1960</v>
       </c>
       <c r="C3" t="n">
-        <v>4999</v>
+        <v>3991</v>
       </c>
       <c r="D3" t="n">
-        <v>9610</v>
+        <v>14842</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2940</v>
+        <v>2281</v>
       </c>
       <c r="C4" t="n">
-        <v>5963</v>
+        <v>5332</v>
       </c>
       <c r="D4" t="n">
-        <v>8650</v>
+        <v>13573</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2528</v>
+        <v>1899</v>
       </c>
       <c r="C5" t="n">
-        <v>6857</v>
+        <v>7993</v>
       </c>
       <c r="D5" t="n">
-        <v>4724</v>
+        <v>6672</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1416</v>
+        <v>1034</v>
       </c>
       <c r="C6" t="n">
-        <v>6251</v>
+        <v>8060</v>
       </c>
       <c r="D6" t="n">
-        <v>1747</v>
+        <v>2108</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>228</v>
       </c>
       <c r="C7" t="n">
-        <v>4738</v>
+        <v>5398</v>
       </c>
       <c r="D7" t="n">
-        <v>706</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>2699</v>
+        <v>2469</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>851</v>
+        <v>636</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
+        <v>124</v>
+      </c>
+      <c r="D11" t="n">
         <v>134</v>
-      </c>
-      <c r="D11" t="n">
-        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3509</v>
+        <v>2712</v>
       </c>
       <c r="C2" t="n">
-        <v>14316</v>
+        <v>10817</v>
       </c>
       <c r="D2" t="n">
-        <v>9227</v>
+        <v>18803</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2370</v>
+        <v>1510</v>
       </c>
       <c r="C3" t="n">
-        <v>3755</v>
+        <v>3406</v>
       </c>
       <c r="D3" t="n">
-        <v>8888</v>
+        <v>13376</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2529</v>
+        <v>1889</v>
       </c>
       <c r="C4" t="n">
-        <v>5422</v>
+        <v>4629</v>
       </c>
       <c r="D4" t="n">
-        <v>8442</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2465</v>
+        <v>1850</v>
       </c>
       <c r="C5" t="n">
-        <v>6345</v>
+        <v>6779</v>
       </c>
       <c r="D5" t="n">
-        <v>5145</v>
+        <v>7396</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1676</v>
+        <v>1223</v>
       </c>
       <c r="C6" t="n">
-        <v>6435</v>
+        <v>8047</v>
       </c>
       <c r="D6" t="n">
-        <v>2124</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>607</v>
+        <v>418</v>
       </c>
       <c r="C7" t="n">
-        <v>5314</v>
+        <v>6334</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>880</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="C8" t="n">
-        <v>3463</v>
+        <v>3443</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1474</v>
+        <v>1216</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>429</v>
+        <v>339</v>
       </c>
       <c r="D10" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6360</v>
+        <v>5029</v>
       </c>
       <c r="C2" t="n">
-        <v>12082</v>
+        <v>10510</v>
       </c>
       <c r="D2" t="n">
-        <v>4560</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2485</v>
+        <v>1980</v>
       </c>
       <c r="C2" t="n">
-        <v>8016</v>
+        <v>6318</v>
       </c>
       <c r="D2" t="n">
-        <v>6791</v>
+        <v>13989</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3153</v>
+        <v>2109</v>
       </c>
       <c r="C3" t="n">
-        <v>6608</v>
+        <v>5356</v>
       </c>
       <c r="D3" t="n">
-        <v>9690</v>
+        <v>14907</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3544</v>
+        <v>2674</v>
       </c>
       <c r="C4" t="n">
-        <v>7525</v>
+        <v>6906</v>
       </c>
       <c r="D4" t="n">
-        <v>8722</v>
+        <v>13433</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1639</v>
+        <v>1147</v>
       </c>
       <c r="C5" t="n">
-        <v>9184</v>
+        <v>10761</v>
       </c>
       <c r="D5" t="n">
-        <v>4794</v>
+        <v>6649</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>560</v>
+        <v>386</v>
       </c>
       <c r="C6" t="n">
-        <v>6532</v>
+        <v>7626</v>
       </c>
       <c r="D6" t="n">
-        <v>1749</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>3393</v>
+        <v>3374</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1444</v>
+        <v>1191</v>
       </c>
       <c r="D8" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>420</v>
+        <v>332</v>
       </c>
       <c r="D9" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8132</v>
+        <v>6695</v>
       </c>
       <c r="C2" t="n">
-        <v>6506</v>
+        <v>6763</v>
       </c>
       <c r="D2" t="n">
-        <v>16770</v>
+        <v>20556</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2702</v>
+        <v>2137</v>
       </c>
       <c r="C3" t="n">
-        <v>6089</v>
+        <v>5297</v>
       </c>
       <c r="D3" t="n">
-        <v>1405</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4557,7 +4557,7 @@
         <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5200</v>
+        <v>4836</v>
       </c>
       <c r="C2" t="n">
-        <v>6045</v>
+        <v>8589</v>
       </c>
       <c r="D2" t="n">
-        <v>16603</v>
+        <v>22295</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4445</v>
+        <v>3623</v>
       </c>
       <c r="C3" t="n">
-        <v>5454</v>
+        <v>5283</v>
       </c>
       <c r="D3" t="n">
-        <v>3882</v>
+        <v>4754</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1208</v>
+        <v>962</v>
       </c>
       <c r="C4" t="n">
-        <v>3611</v>
+        <v>3146</v>
       </c>
       <c r="D4" t="n">
-        <v>1464</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="5">
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
         <v>853</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4689</v>
+        <v>5138</v>
       </c>
       <c r="C2" t="n">
-        <v>8927</v>
+        <v>5756</v>
       </c>
       <c r="D2" t="n">
-        <v>14882</v>
+        <v>35142</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3969</v>
+        <v>3469</v>
       </c>
       <c r="C3" t="n">
-        <v>5003</v>
+        <v>6115</v>
       </c>
       <c r="D3" t="n">
-        <v>5637</v>
+        <v>7218</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2401</v>
+        <v>1946</v>
       </c>
       <c r="C4" t="n">
-        <v>4527</v>
+        <v>4240</v>
       </c>
       <c r="D4" t="n">
-        <v>1883</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>545</v>
+        <v>447</v>
       </c>
       <c r="C5" t="n">
-        <v>2072</v>
+        <v>1817</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="6">
@@ -5193,7 +5193,7 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D6" t="n">
         <v>903</v>
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D7" t="n">
         <v>629</v>
@@ -5319,7 +5319,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,7 +5333,7 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5961</v>
+        <v>5353</v>
       </c>
       <c r="C2" t="n">
-        <v>7383</v>
+        <v>12098</v>
       </c>
       <c r="D2" t="n">
-        <v>22542</v>
+        <v>41099</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3551</v>
+        <v>3486</v>
       </c>
       <c r="C3" t="n">
-        <v>6160</v>
+        <v>5174</v>
       </c>
       <c r="D3" t="n">
-        <v>6645</v>
+        <v>10954</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2680</v>
+        <v>2271</v>
       </c>
       <c r="C4" t="n">
-        <v>4640</v>
+        <v>5101</v>
       </c>
       <c r="D4" t="n">
-        <v>2510</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1207</v>
+        <v>981</v>
       </c>
       <c r="C5" t="n">
-        <v>3301</v>
+        <v>3035</v>
       </c>
       <c r="D5" t="n">
-        <v>1268</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>295</v>
+        <v>256</v>
       </c>
       <c r="C6" t="n">
-        <v>1180</v>
+        <v>1056</v>
       </c>
       <c r="D6" t="n">
-        <v>941</v>
+        <v>943</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8">
@@ -5535,7 +5535,7 @@
         <v>379</v>
       </c>
       <c r="D8" t="n">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,10 +5543,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>381</v>
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
         <v>189</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
         <v>101</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6843</v>
+        <v>5791</v>
       </c>
       <c r="C2" t="n">
-        <v>5089</v>
+        <v>13269</v>
       </c>
       <c r="D2" t="n">
-        <v>18933</v>
+        <v>32597</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3452</v>
+        <v>3175</v>
       </c>
       <c r="C3" t="n">
-        <v>5552</v>
+        <v>7085</v>
       </c>
       <c r="D3" t="n">
-        <v>8084</v>
+        <v>13889</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1913</v>
+        <v>1763</v>
       </c>
       <c r="C4" t="n">
-        <v>4434</v>
+        <v>4205</v>
       </c>
       <c r="D4" t="n">
-        <v>2780</v>
+        <v>3785</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1005</v>
+        <v>843</v>
       </c>
       <c r="C5" t="n">
-        <v>2914</v>
+        <v>2960</v>
       </c>
       <c r="D5" t="n">
-        <v>1159</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>352</v>
+        <v>285</v>
       </c>
       <c r="C6" t="n">
-        <v>1500</v>
+        <v>1369</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>755</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>476</v>
+        <v>440</v>
       </c>
       <c r="D7" t="n">
-        <v>514</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>354</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
@@ -5871,7 +5871,7 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D10" t="n">
         <v>233</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5898</v>
+        <v>4310</v>
       </c>
       <c r="C2" t="n">
-        <v>2709</v>
+        <v>7717</v>
       </c>
       <c r="D2" t="n">
-        <v>21680</v>
+        <v>25140</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4258</v>
+        <v>3688</v>
       </c>
       <c r="C3" t="n">
-        <v>4536</v>
+        <v>9166</v>
       </c>
       <c r="D3" t="n">
-        <v>9311</v>
+        <v>16009</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2328</v>
+        <v>2130</v>
       </c>
       <c r="C4" t="n">
-        <v>5017</v>
+        <v>5831</v>
       </c>
       <c r="D4" t="n">
-        <v>3738</v>
+        <v>5706</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1304</v>
+        <v>1156</v>
       </c>
       <c r="C5" t="n">
-        <v>3743</v>
+        <v>3615</v>
       </c>
       <c r="D5" t="n">
-        <v>1450</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>627</v>
+        <v>513</v>
       </c>
       <c r="C6" t="n">
-        <v>2282</v>
+        <v>2238</v>
       </c>
       <c r="D6" t="n">
-        <v>824</v>
+        <v>841</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>167</v>
       </c>
       <c r="C7" t="n">
-        <v>1047</v>
+        <v>949</v>
       </c>
       <c r="D7" t="n">
-        <v>549</v>
+        <v>560</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>359</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4442</v>
+        <v>3695</v>
       </c>
       <c r="C2" t="n">
-        <v>2437</v>
+        <v>7693</v>
       </c>
       <c r="D2" t="n">
-        <v>16542</v>
+        <v>28873</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4162</v>
+        <v>3285</v>
       </c>
       <c r="C3" t="n">
-        <v>3085</v>
+        <v>7302</v>
       </c>
       <c r="D3" t="n">
-        <v>10619</v>
+        <v>16269</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2828</v>
+        <v>2456</v>
       </c>
       <c r="C4" t="n">
-        <v>4596</v>
+        <v>7534</v>
       </c>
       <c r="D4" t="n">
-        <v>4694</v>
+        <v>7357</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1582</v>
+        <v>1432</v>
       </c>
       <c r="C5" t="n">
-        <v>4362</v>
+        <v>4709</v>
       </c>
       <c r="D5" t="n">
-        <v>1809</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>878</v>
+        <v>740</v>
       </c>
       <c r="C6" t="n">
-        <v>3027</v>
+        <v>2892</v>
       </c>
       <c r="D6" t="n">
-        <v>926</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>360</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>1688</v>
+        <v>1605</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="C8" t="n">
-        <v>699</v>
+        <v>636</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="D9" t="n">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>112</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>42</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_42_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4670</v>
+        <v>5423</v>
       </c>
       <c r="C2" t="n">
-        <v>7193</v>
+        <v>6546</v>
       </c>
       <c r="D2" t="n">
-        <v>37189</v>
+        <v>32907</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2866</v>
+        <v>3716</v>
       </c>
       <c r="C3" t="n">
-        <v>6565</v>
+        <v>6988</v>
       </c>
       <c r="D3" t="n">
-        <v>16964</v>
+        <v>16766</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2417</v>
+        <v>2672</v>
       </c>
       <c r="C4" t="n">
-        <v>7261</v>
+        <v>6050</v>
       </c>
       <c r="D4" t="n">
-        <v>8673</v>
+        <v>8522</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1672</v>
+        <v>1768</v>
       </c>
       <c r="C5" t="n">
-        <v>5921</v>
+        <v>4868</v>
       </c>
       <c r="D5" t="n">
-        <v>3093</v>
+        <v>3385</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>946</v>
+        <v>1021</v>
       </c>
       <c r="C6" t="n">
-        <v>3717</v>
+        <v>2536</v>
       </c>
       <c r="D6" t="n">
-        <v>1184</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>435</v>
+        <v>476</v>
       </c>
       <c r="C7" t="n">
-        <v>2181</v>
+        <v>1199</v>
       </c>
       <c r="D7" t="n">
-        <v>654</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>1072</v>
+        <v>546</v>
       </c>
       <c r="D8" t="n">
-        <v>423</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>422</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5298</v>
+        <v>6224</v>
       </c>
       <c r="C2" t="n">
-        <v>5903</v>
+        <v>6729</v>
       </c>
       <c r="D2" t="n">
-        <v>32700</v>
+        <v>36468</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2946</v>
+        <v>3658</v>
       </c>
       <c r="C3" t="n">
-        <v>6044</v>
+        <v>5972</v>
       </c>
       <c r="D3" t="n">
-        <v>18439</v>
+        <v>17834</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2229</v>
+        <v>2695</v>
       </c>
       <c r="C4" t="n">
-        <v>6726</v>
+        <v>6316</v>
       </c>
       <c r="D4" t="n">
-        <v>9682</v>
+        <v>9608</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>1907</v>
       </c>
       <c r="C5" t="n">
-        <v>6389</v>
+        <v>5322</v>
       </c>
       <c r="D5" t="n">
-        <v>3772</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1139</v>
+        <v>1222</v>
       </c>
       <c r="C6" t="n">
-        <v>4577</v>
+        <v>3538</v>
       </c>
       <c r="D6" t="n">
-        <v>1431</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>571</v>
+        <v>639</v>
       </c>
       <c r="C7" t="n">
-        <v>2827</v>
+        <v>1801</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>761</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>236</v>
+        <v>265</v>
       </c>
       <c r="C8" t="n">
-        <v>1506</v>
+        <v>822</v>
       </c>
       <c r="D8" t="n">
-        <v>446</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>672</v>
+        <v>389</v>
       </c>
       <c r="D9" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6464</v>
+        <v>9063</v>
       </c>
       <c r="C2" t="n">
-        <v>10903</v>
+        <v>10955</v>
       </c>
       <c r="D2" t="n">
-        <v>31131</v>
+        <v>31948</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3157</v>
+        <v>3824</v>
       </c>
       <c r="C3" t="n">
-        <v>5337</v>
+        <v>5572</v>
       </c>
       <c r="D3" t="n">
-        <v>19147</v>
+        <v>19049</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2131</v>
+        <v>2630</v>
       </c>
       <c r="C4" t="n">
-        <v>6304</v>
+        <v>6032</v>
       </c>
       <c r="D4" t="n">
-        <v>10471</v>
+        <v>10579</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1732</v>
+        <v>1977</v>
       </c>
       <c r="C5" t="n">
-        <v>6327</v>
+        <v>5580</v>
       </c>
       <c r="D5" t="n">
-        <v>4415</v>
+        <v>4678</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1250</v>
+        <v>1379</v>
       </c>
       <c r="C6" t="n">
-        <v>5189</v>
+        <v>4207</v>
       </c>
       <c r="D6" t="n">
-        <v>1727</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>700</v>
+        <v>779</v>
       </c>
       <c r="C7" t="n">
-        <v>3494</v>
+        <v>2515</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>861</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>316</v>
+        <v>361</v>
       </c>
       <c r="C8" t="n">
-        <v>1969</v>
+        <v>1197</v>
       </c>
       <c r="D8" t="n">
-        <v>476</v>
+        <v>503</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>959</v>
+        <v>554</v>
       </c>
       <c r="D9" t="n">
-        <v>326</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>422</v>
+        <v>285</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5930</v>
+        <v>8073</v>
       </c>
       <c r="C2" t="n">
-        <v>7675</v>
+        <v>7449</v>
       </c>
       <c r="D2" t="n">
-        <v>25823</v>
+        <v>26289</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3752</v>
+        <v>4684</v>
       </c>
       <c r="C3" t="n">
-        <v>8893</v>
+        <v>9095</v>
       </c>
       <c r="D3" t="n">
-        <v>20779</v>
+        <v>20805</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1600</v>
+        <v>1826</v>
       </c>
       <c r="C4" t="n">
-        <v>9402</v>
+        <v>8715</v>
       </c>
       <c r="D4" t="n">
-        <v>9828</v>
+        <v>10139</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1155</v>
+        <v>1274</v>
       </c>
       <c r="C5" t="n">
-        <v>5085</v>
+        <v>4122</v>
       </c>
       <c r="D5" t="n">
-        <v>2836</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>646</v>
+        <v>719</v>
       </c>
       <c r="C6" t="n">
-        <v>3424</v>
+        <v>2464</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>291</v>
+        <v>333</v>
       </c>
       <c r="C7" t="n">
-        <v>1929</v>
+        <v>1173</v>
       </c>
       <c r="D7" t="n">
-        <v>466</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>939</v>
+        <v>542</v>
       </c>
       <c r="D8" t="n">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>413</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>30</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3560</v>
+        <v>4854</v>
       </c>
       <c r="C2" t="n">
-        <v>3418</v>
+        <v>3323</v>
       </c>
       <c r="D2" t="n">
-        <v>18770</v>
+        <v>19276</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4023</v>
+        <v>5217</v>
       </c>
       <c r="C3" t="n">
-        <v>7618</v>
+        <v>7551</v>
       </c>
       <c r="D3" t="n">
-        <v>20261</v>
+        <v>20352</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2072</v>
+        <v>2523</v>
       </c>
       <c r="C4" t="n">
-        <v>9252</v>
+        <v>9047</v>
       </c>
       <c r="D4" t="n">
-        <v>11294</v>
+        <v>11663</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1401</v>
       </c>
       <c r="C5" t="n">
-        <v>6922</v>
+        <v>6130</v>
       </c>
       <c r="D5" t="n">
-        <v>3609</v>
+        <v>3989</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>759</v>
+        <v>863</v>
       </c>
       <c r="C6" t="n">
-        <v>4142</v>
+        <v>3163</v>
       </c>
       <c r="D6" t="n">
-        <v>974</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>2479</v>
+        <v>1630</v>
       </c>
       <c r="D7" t="n">
-        <v>510</v>
+        <v>539</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>1221</v>
+        <v>724</v>
       </c>
       <c r="D8" t="n">
-        <v>325</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>449</v>
+        <v>328</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>33</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>29</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3331</v>
+        <v>5698</v>
       </c>
       <c r="C2" t="n">
-        <v>5311</v>
+        <v>3744</v>
       </c>
       <c r="D2" t="n">
-        <v>17406</v>
+        <v>24655</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3224</v>
+        <v>4292</v>
       </c>
       <c r="C3" t="n">
-        <v>5096</v>
+        <v>4934</v>
       </c>
       <c r="D3" t="n">
-        <v>18891</v>
+        <v>18992</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>3133</v>
       </c>
       <c r="C4" t="n">
-        <v>8290</v>
+        <v>8126</v>
       </c>
       <c r="D4" t="n">
-        <v>12219</v>
+        <v>12726</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1416</v>
+        <v>1666</v>
       </c>
       <c r="C5" t="n">
-        <v>7829</v>
+        <v>7374</v>
       </c>
       <c r="D5" t="n">
-        <v>4679</v>
+        <v>5046</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>877</v>
+        <v>1008</v>
       </c>
       <c r="C6" t="n">
-        <v>5344</v>
+        <v>4501</v>
       </c>
       <c r="D6" t="n">
-        <v>1340</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>399</v>
+        <v>461</v>
       </c>
       <c r="C7" t="n">
-        <v>3186</v>
+        <v>2306</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="C8" t="n">
-        <v>1713</v>
+        <v>1094</v>
       </c>
       <c r="D8" t="n">
-        <v>348</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>725</v>
+        <v>478</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
         <v>185</v>
       </c>
       <c r="D11" t="n">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,10 +2489,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2017</v>
+        <v>3352</v>
       </c>
       <c r="C2" t="n">
-        <v>2612</v>
+        <v>1802</v>
       </c>
       <c r="D2" t="n">
-        <v>12156</v>
+        <v>17185</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3136</v>
+        <v>4503</v>
       </c>
       <c r="C3" t="n">
-        <v>5026</v>
+        <v>4384</v>
       </c>
       <c r="D3" t="n">
-        <v>18313</v>
+        <v>19155</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2732</v>
+        <v>3452</v>
       </c>
       <c r="C4" t="n">
-        <v>7932</v>
+        <v>7695</v>
       </c>
       <c r="D4" t="n">
-        <v>13100</v>
+        <v>13539</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1490</v>
+        <v>1753</v>
       </c>
       <c r="C5" t="n">
-        <v>9248</v>
+        <v>8705</v>
       </c>
       <c r="D5" t="n">
-        <v>4911</v>
+        <v>5322</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>709</v>
+        <v>835</v>
       </c>
       <c r="C6" t="n">
-        <v>6157</v>
+        <v>5223</v>
       </c>
       <c r="D6" t="n">
-        <v>1294</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>3252</v>
+        <v>2276</v>
       </c>
       <c r="D7" t="n">
-        <v>567</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1197</v>
+        <v>800</v>
       </c>
       <c r="D8" t="n">
-        <v>369</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>295</v>
+        <v>252</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>181</v>
       </c>
       <c r="D10" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>30</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2126</v>
+        <v>3437</v>
       </c>
       <c r="C2" t="n">
-        <v>5641</v>
+        <v>1748</v>
       </c>
       <c r="D2" t="n">
-        <v>10799</v>
+        <v>23263</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2285</v>
+        <v>3439</v>
       </c>
       <c r="C3" t="n">
-        <v>3560</v>
+        <v>2867</v>
       </c>
       <c r="D3" t="n">
-        <v>16323</v>
+        <v>17783</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2551</v>
+        <v>3407</v>
       </c>
       <c r="C4" t="n">
-        <v>6455</v>
+        <v>6051</v>
       </c>
       <c r="D4" t="n">
-        <v>13502</v>
+        <v>13990</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1755</v>
+        <v>2147</v>
       </c>
       <c r="C5" t="n">
-        <v>8575</v>
+        <v>8161</v>
       </c>
       <c r="D5" t="n">
-        <v>5940</v>
+        <v>6343</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>904</v>
+        <v>1065</v>
       </c>
       <c r="C6" t="n">
-        <v>7409</v>
+        <v>6664</v>
       </c>
       <c r="D6" t="n">
-        <v>1775</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>4424</v>
+        <v>3452</v>
       </c>
       <c r="D7" t="n">
-        <v>646</v>
+        <v>707</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1924</v>
+        <v>1358</v>
       </c>
       <c r="D8" t="n">
-        <v>390</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>577</v>
+        <v>428</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1458</v>
+        <v>2346</v>
       </c>
       <c r="C2" t="n">
-        <v>3442</v>
+        <v>2059</v>
       </c>
       <c r="D2" t="n">
-        <v>9356</v>
+        <v>16230</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1960</v>
+        <v>3013</v>
       </c>
       <c r="C3" t="n">
-        <v>3991</v>
+        <v>2211</v>
       </c>
       <c r="D3" t="n">
-        <v>14842</v>
+        <v>17643</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2281</v>
+        <v>3143</v>
       </c>
       <c r="C4" t="n">
-        <v>5332</v>
+        <v>4815</v>
       </c>
       <c r="D4" t="n">
-        <v>13573</v>
+        <v>14172</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1899</v>
+        <v>2384</v>
       </c>
       <c r="C5" t="n">
-        <v>7993</v>
+        <v>7555</v>
       </c>
       <c r="D5" t="n">
-        <v>6672</v>
+        <v>7018</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1034</v>
+        <v>1245</v>
       </c>
       <c r="C6" t="n">
-        <v>8060</v>
+        <v>7392</v>
       </c>
       <c r="D6" t="n">
-        <v>2108</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>228</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>5398</v>
+        <v>4409</v>
       </c>
       <c r="D7" t="n">
-        <v>725</v>
+        <v>793</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2469</v>
+        <v>1839</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>636</v>
+        <v>496</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>178</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2712</v>
+        <v>3632</v>
       </c>
       <c r="C2" t="n">
-        <v>10817</v>
+        <v>10992</v>
       </c>
       <c r="D2" t="n">
-        <v>18803</v>
+        <v>29934</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1510</v>
+        <v>2337</v>
       </c>
       <c r="C3" t="n">
-        <v>3406</v>
+        <v>1913</v>
       </c>
       <c r="D3" t="n">
-        <v>13376</v>
+        <v>16344</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1889</v>
+        <v>2718</v>
       </c>
       <c r="C4" t="n">
-        <v>4629</v>
+        <v>3614</v>
       </c>
       <c r="D4" t="n">
-        <v>13200</v>
+        <v>14240</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1850</v>
+        <v>2403</v>
       </c>
       <c r="C5" t="n">
-        <v>6779</v>
+        <v>6293</v>
       </c>
       <c r="D5" t="n">
-        <v>7396</v>
+        <v>7766</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1223</v>
+        <v>1511</v>
       </c>
       <c r="C6" t="n">
-        <v>8047</v>
+        <v>7392</v>
       </c>
       <c r="D6" t="n">
-        <v>2650</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>518</v>
       </c>
       <c r="C7" t="n">
-        <v>6334</v>
+        <v>5561</v>
       </c>
       <c r="D7" t="n">
-        <v>880</v>
+        <v>968</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C8" t="n">
-        <v>3443</v>
+        <v>2719</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
-        <v>1216</v>
+        <v>934</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>339</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>39</v>
+      </c>
+      <c r="D14" t="n">
         <v>38</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5029</v>
+        <v>4761</v>
       </c>
       <c r="C2" t="n">
-        <v>10510</v>
+        <v>2683</v>
       </c>
       <c r="D2" t="n">
-        <v>6403</v>
+        <v>16145</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1980</v>
+        <v>2628</v>
       </c>
       <c r="C2" t="n">
-        <v>6318</v>
+        <v>6331</v>
       </c>
       <c r="D2" t="n">
-        <v>13989</v>
+        <v>22270</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2109</v>
+        <v>3161</v>
       </c>
       <c r="C3" t="n">
-        <v>5356</v>
+        <v>4115</v>
       </c>
       <c r="D3" t="n">
-        <v>14907</v>
+        <v>18323</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2674</v>
+        <v>3611</v>
       </c>
       <c r="C4" t="n">
-        <v>6906</v>
+        <v>5646</v>
       </c>
       <c r="D4" t="n">
-        <v>13433</v>
+        <v>14577</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1147</v>
+        <v>1440</v>
       </c>
       <c r="C5" t="n">
-        <v>10761</v>
+        <v>9915</v>
       </c>
       <c r="D5" t="n">
-        <v>6649</v>
+        <v>7016</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>386</v>
+        <v>478</v>
       </c>
       <c r="C6" t="n">
-        <v>7626</v>
+        <v>6826</v>
       </c>
       <c r="D6" t="n">
-        <v>2022</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C7" t="n">
-        <v>3374</v>
+        <v>2664</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>566</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1191</v>
+        <v>915</v>
       </c>
       <c r="D8" t="n">
-        <v>287</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>332</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" t="n">
         <v>37</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6695</v>
+        <v>7146</v>
       </c>
       <c r="C2" t="n">
-        <v>6763</v>
+        <v>5167</v>
       </c>
       <c r="D2" t="n">
-        <v>20556</v>
+        <v>19660</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2137</v>
+        <v>2024</v>
       </c>
       <c r="C3" t="n">
-        <v>5297</v>
+        <v>1352</v>
       </c>
       <c r="D3" t="n">
-        <v>1715</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C6" t="n">
         <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>816</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>538</v>
       </c>
     </row>
     <row r="8">
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4836</v>
+        <v>5210</v>
       </c>
       <c r="C2" t="n">
-        <v>8589</v>
+        <v>4366</v>
       </c>
       <c r="D2" t="n">
-        <v>22295</v>
+        <v>22147</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3623</v>
+        <v>3760</v>
       </c>
       <c r="C3" t="n">
-        <v>5283</v>
+        <v>3027</v>
       </c>
       <c r="D3" t="n">
-        <v>4754</v>
+        <v>5844</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>962</v>
+        <v>913</v>
       </c>
       <c r="C4" t="n">
-        <v>3146</v>
+        <v>836</v>
       </c>
       <c r="D4" t="n">
-        <v>1526</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D6" t="n">
-        <v>853</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
         <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
         <v>352</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5022,10 +5022,10 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5138</v>
+        <v>4669</v>
       </c>
       <c r="C2" t="n">
-        <v>5756</v>
+        <v>4814</v>
       </c>
       <c r="D2" t="n">
-        <v>35142</v>
+        <v>33713</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3469</v>
+        <v>3676</v>
       </c>
       <c r="C3" t="n">
-        <v>6115</v>
+        <v>3252</v>
       </c>
       <c r="D3" t="n">
-        <v>7218</v>
+        <v>8031</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1946</v>
+        <v>1974</v>
       </c>
       <c r="C4" t="n">
-        <v>4240</v>
+        <v>2059</v>
       </c>
       <c r="D4" t="n">
-        <v>2099</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="C5" t="n">
-        <v>1817</v>
+        <v>550</v>
       </c>
       <c r="D5" t="n">
-        <v>1209</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>903</v>
+        <v>915</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>629</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14">
@@ -5316,10 +5316,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5353</v>
+        <v>5248</v>
       </c>
       <c r="C2" t="n">
-        <v>12098</v>
+        <v>11348</v>
       </c>
       <c r="D2" t="n">
-        <v>41099</v>
+        <v>33488</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3486</v>
+        <v>3415</v>
       </c>
       <c r="C3" t="n">
-        <v>5174</v>
+        <v>3568</v>
       </c>
       <c r="D3" t="n">
-        <v>10954</v>
+        <v>11369</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2271</v>
+        <v>2380</v>
       </c>
       <c r="C4" t="n">
-        <v>5101</v>
+        <v>2637</v>
       </c>
       <c r="D4" t="n">
-        <v>2968</v>
+        <v>3459</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>981</v>
+        <v>999</v>
       </c>
       <c r="C5" t="n">
-        <v>3035</v>
+        <v>1335</v>
       </c>
       <c r="D5" t="n">
-        <v>1314</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C6" t="n">
-        <v>1056</v>
+        <v>425</v>
       </c>
       <c r="D6" t="n">
-        <v>943</v>
+        <v>961</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D7" t="n">
-        <v>668</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D9" t="n">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="n">
         <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,7 +5574,7 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="14">
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5791</v>
+        <v>6298</v>
       </c>
       <c r="C2" t="n">
-        <v>13269</v>
+        <v>10577</v>
       </c>
       <c r="D2" t="n">
-        <v>32597</v>
+        <v>27993</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3175</v>
+        <v>3147</v>
       </c>
       <c r="C3" t="n">
-        <v>7085</v>
+        <v>6238</v>
       </c>
       <c r="D3" t="n">
-        <v>13889</v>
+        <v>13105</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1763</v>
+        <v>1811</v>
       </c>
       <c r="C4" t="n">
-        <v>4205</v>
+        <v>2591</v>
       </c>
       <c r="D4" t="n">
-        <v>3785</v>
+        <v>4158</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>843</v>
+        <v>877</v>
       </c>
       <c r="C5" t="n">
-        <v>2960</v>
+        <v>1480</v>
       </c>
       <c r="D5" t="n">
-        <v>1263</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>285</v>
+        <v>298</v>
       </c>
       <c r="C6" t="n">
-        <v>1369</v>
+        <v>592</v>
       </c>
       <c r="D6" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>87</v>
       </c>
       <c r="C7" t="n">
-        <v>440</v>
+        <v>248</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -5980,7 +5980,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
         <v>33</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4310</v>
+        <v>4854</v>
       </c>
       <c r="C2" t="n">
-        <v>7717</v>
+        <v>6626</v>
       </c>
       <c r="D2" t="n">
-        <v>25140</v>
+        <v>22286</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3688</v>
+        <v>3930</v>
       </c>
       <c r="C3" t="n">
-        <v>9166</v>
+        <v>7571</v>
       </c>
       <c r="D3" t="n">
-        <v>16009</v>
+        <v>14739</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2130</v>
+        <v>2161</v>
       </c>
       <c r="C4" t="n">
-        <v>5831</v>
+        <v>4777</v>
       </c>
       <c r="D4" t="n">
-        <v>5706</v>
+        <v>5921</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1156</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="n">
-        <v>3615</v>
+        <v>2110</v>
       </c>
       <c r="D5" t="n">
-        <v>1696</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>513</v>
+        <v>548</v>
       </c>
       <c r="C6" t="n">
-        <v>2238</v>
+        <v>1096</v>
       </c>
       <c r="D6" t="n">
-        <v>841</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>949</v>
+        <v>443</v>
       </c>
       <c r="D7" t="n">
-        <v>560</v>
+        <v>568</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>336</v>
+        <v>236</v>
       </c>
       <c r="D8" t="n">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3695</v>
+        <v>5579</v>
       </c>
       <c r="C2" t="n">
-        <v>7693</v>
+        <v>9906</v>
       </c>
       <c r="D2" t="n">
-        <v>28873</v>
+        <v>34160</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3285</v>
+        <v>3615</v>
       </c>
       <c r="C3" t="n">
-        <v>7302</v>
+        <v>6087</v>
       </c>
       <c r="D3" t="n">
-        <v>16269</v>
+        <v>14885</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2456</v>
+        <v>2631</v>
       </c>
       <c r="C4" t="n">
-        <v>7534</v>
+        <v>6286</v>
       </c>
       <c r="D4" t="n">
-        <v>7357</v>
+        <v>7377</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1432</v>
+        <v>1486</v>
       </c>
       <c r="C5" t="n">
-        <v>4709</v>
+        <v>3551</v>
       </c>
       <c r="D5" t="n">
-        <v>2375</v>
+        <v>2649</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>740</v>
+        <v>791</v>
       </c>
       <c r="C6" t="n">
-        <v>2892</v>
+        <v>1628</v>
       </c>
       <c r="D6" t="n">
-        <v>968</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="C7" t="n">
-        <v>1605</v>
+        <v>788</v>
       </c>
       <c r="D7" t="n">
-        <v>603</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
-        <v>636</v>
+        <v>339</v>
       </c>
       <c r="D8" t="n">
-        <v>402</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="D9" t="n">
         <v>292</v>
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_42_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_42_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5423</v>
+        <v>1229</v>
       </c>
       <c r="C2" t="n">
-        <v>6546</v>
+        <v>3154</v>
       </c>
       <c r="D2" t="n">
-        <v>32907</v>
+        <v>19238</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3716</v>
+        <v>2333</v>
       </c>
       <c r="C3" t="n">
-        <v>6988</v>
+        <v>7359</v>
       </c>
       <c r="D3" t="n">
-        <v>16766</v>
+        <v>14489</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2672</v>
+        <v>1542</v>
       </c>
       <c r="C4" t="n">
-        <v>6050</v>
+        <v>7543</v>
       </c>
       <c r="D4" t="n">
-        <v>8522</v>
+        <v>6163</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1768</v>
+        <v>710</v>
       </c>
       <c r="C5" t="n">
-        <v>4868</v>
+        <v>3863</v>
       </c>
       <c r="D5" t="n">
-        <v>3385</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1021</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>2536</v>
+        <v>1489</v>
       </c>
       <c r="D6" t="n">
-        <v>1305</v>
+        <v>746</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>476</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>1199</v>
+        <v>567</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>493</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>546</v>
+        <v>339</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>142</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6224</v>
+        <v>1377</v>
       </c>
       <c r="C2" t="n">
-        <v>6729</v>
+        <v>10395</v>
       </c>
       <c r="D2" t="n">
-        <v>36468</v>
+        <v>18565</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3658</v>
+        <v>1525</v>
       </c>
       <c r="C3" t="n">
-        <v>5972</v>
+        <v>4430</v>
       </c>
       <c r="D3" t="n">
-        <v>17834</v>
+        <v>14344</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2695</v>
+        <v>1669</v>
       </c>
       <c r="C4" t="n">
-        <v>6316</v>
+        <v>7356</v>
       </c>
       <c r="D4" t="n">
-        <v>9608</v>
+        <v>7494</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1907</v>
+        <v>965</v>
       </c>
       <c r="C5" t="n">
-        <v>5322</v>
+        <v>5762</v>
       </c>
       <c r="D5" t="n">
-        <v>4038</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1222</v>
+        <v>451</v>
       </c>
       <c r="C6" t="n">
-        <v>3538</v>
+        <v>2658</v>
       </c>
       <c r="D6" t="n">
-        <v>1607</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>639</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1801</v>
+        <v>1024</v>
       </c>
       <c r="D7" t="n">
-        <v>761</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>265</v>
+        <v>81</v>
       </c>
       <c r="C8" t="n">
-        <v>822</v>
+        <v>450</v>
       </c>
       <c r="D8" t="n">
-        <v>468</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>389</v>
+        <v>314</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="D10" t="n">
-        <v>251</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9063</v>
+        <v>722</v>
       </c>
       <c r="C2" t="n">
-        <v>10955</v>
+        <v>4269</v>
       </c>
       <c r="D2" t="n">
-        <v>31948</v>
+        <v>12543</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3824</v>
+        <v>1425</v>
       </c>
       <c r="C3" t="n">
-        <v>5572</v>
+        <v>6583</v>
       </c>
       <c r="D3" t="n">
-        <v>19049</v>
+        <v>14494</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2630</v>
+        <v>1815</v>
       </c>
       <c r="C4" t="n">
-        <v>6032</v>
+        <v>6757</v>
       </c>
       <c r="D4" t="n">
-        <v>10579</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1977</v>
+        <v>970</v>
       </c>
       <c r="C5" t="n">
-        <v>5580</v>
+        <v>6915</v>
       </c>
       <c r="D5" t="n">
-        <v>4678</v>
+        <v>3129</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1379</v>
+        <v>364</v>
       </c>
       <c r="C6" t="n">
-        <v>4207</v>
+        <v>3539</v>
       </c>
       <c r="D6" t="n">
-        <v>1935</v>
+        <v>968</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>779</v>
+        <v>74</v>
       </c>
       <c r="C7" t="n">
-        <v>2515</v>
+        <v>1010</v>
       </c>
       <c r="D7" t="n">
-        <v>861</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>361</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>1197</v>
+        <v>470</v>
       </c>
       <c r="D8" t="n">
-        <v>503</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>241</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>371</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>285</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>257</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>196</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>207</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>118</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D18" t="n">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8073</v>
+        <v>607</v>
       </c>
       <c r="C2" t="n">
-        <v>7449</v>
+        <v>4397</v>
       </c>
       <c r="D2" t="n">
-        <v>26289</v>
+        <v>11337</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4684</v>
+        <v>945</v>
       </c>
       <c r="C3" t="n">
-        <v>9095</v>
+        <v>4756</v>
       </c>
       <c r="D3" t="n">
-        <v>20805</v>
+        <v>13177</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1826</v>
+        <v>1446</v>
       </c>
       <c r="C4" t="n">
-        <v>8715</v>
+        <v>6589</v>
       </c>
       <c r="D4" t="n">
-        <v>10139</v>
+        <v>9348</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1274</v>
+        <v>1207</v>
       </c>
       <c r="C5" t="n">
-        <v>4122</v>
+        <v>6758</v>
       </c>
       <c r="D5" t="n">
-        <v>3153</v>
+        <v>3896</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>719</v>
+        <v>554</v>
       </c>
       <c r="C6" t="n">
-        <v>2464</v>
+        <v>5125</v>
       </c>
       <c r="D6" t="n">
-        <v>843</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>333</v>
+        <v>155</v>
       </c>
       <c r="C7" t="n">
-        <v>1173</v>
+        <v>2169</v>
       </c>
       <c r="D7" t="n">
-        <v>492</v>
+        <v>615</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>56</v>
       </c>
       <c r="C8" t="n">
-        <v>542</v>
+        <v>705</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>449</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="D9" t="n">
-        <v>251</v>
+        <v>377</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>202</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D17" t="n">
-        <v>39</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4854</v>
+        <v>486</v>
       </c>
       <c r="C2" t="n">
-        <v>3323</v>
+        <v>2539</v>
       </c>
       <c r="D2" t="n">
-        <v>19276</v>
+        <v>8599</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5217</v>
+        <v>714</v>
       </c>
       <c r="C3" t="n">
-        <v>7551</v>
+        <v>4122</v>
       </c>
       <c r="D3" t="n">
-        <v>20352</v>
+        <v>12167</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2523</v>
+        <v>1176</v>
       </c>
       <c r="C4" t="n">
-        <v>9047</v>
+        <v>5779</v>
       </c>
       <c r="D4" t="n">
-        <v>11663</v>
+        <v>9741</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1401</v>
+        <v>1259</v>
       </c>
       <c r="C5" t="n">
-        <v>6130</v>
+        <v>6805</v>
       </c>
       <c r="D5" t="n">
-        <v>3989</v>
+        <v>4585</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>863</v>
+        <v>692</v>
       </c>
       <c r="C6" t="n">
-        <v>3163</v>
+        <v>5981</v>
       </c>
       <c r="D6" t="n">
-        <v>1079</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>174</v>
       </c>
       <c r="C7" t="n">
-        <v>1630</v>
+        <v>3185</v>
       </c>
       <c r="D7" t="n">
-        <v>539</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>724</v>
+        <v>1068</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>328</v>
+        <v>430</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>375</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D16" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5698</v>
+        <v>788</v>
       </c>
       <c r="C2" t="n">
-        <v>3744</v>
+        <v>13588</v>
       </c>
       <c r="D2" t="n">
-        <v>24655</v>
+        <v>12853</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4292</v>
+        <v>522</v>
       </c>
       <c r="C3" t="n">
-        <v>4934</v>
+        <v>3014</v>
       </c>
       <c r="D3" t="n">
-        <v>18992</v>
+        <v>10864</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3133</v>
+        <v>860</v>
       </c>
       <c r="C4" t="n">
-        <v>8126</v>
+        <v>4863</v>
       </c>
       <c r="D4" t="n">
-        <v>12726</v>
+        <v>9840</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1666</v>
+        <v>1135</v>
       </c>
       <c r="C5" t="n">
-        <v>7374</v>
+        <v>6190</v>
       </c>
       <c r="D5" t="n">
-        <v>5046</v>
+        <v>5237</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1008</v>
+        <v>847</v>
       </c>
       <c r="C6" t="n">
-        <v>4501</v>
+        <v>6346</v>
       </c>
       <c r="D6" t="n">
-        <v>1483</v>
+        <v>1994</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>461</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>2306</v>
+        <v>4361</v>
       </c>
       <c r="D7" t="n">
-        <v>607</v>
+        <v>794</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>159</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1094</v>
+        <v>1928</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>502</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>671</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>383</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>89</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3352</v>
+        <v>529</v>
       </c>
       <c r="C2" t="n">
-        <v>1802</v>
+        <v>7065</v>
       </c>
       <c r="D2" t="n">
-        <v>17185</v>
+        <v>9255</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4503</v>
+        <v>787</v>
       </c>
       <c r="C3" t="n">
-        <v>4384</v>
+        <v>6206</v>
       </c>
       <c r="D3" t="n">
-        <v>19155</v>
+        <v>11930</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3452</v>
+        <v>1466</v>
       </c>
       <c r="C4" t="n">
-        <v>7695</v>
+        <v>6764</v>
       </c>
       <c r="D4" t="n">
-        <v>13539</v>
+        <v>10130</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1753</v>
+        <v>856</v>
       </c>
       <c r="C5" t="n">
-        <v>8705</v>
+        <v>9002</v>
       </c>
       <c r="D5" t="n">
-        <v>5322</v>
+        <v>4809</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>835</v>
+        <v>300</v>
       </c>
       <c r="C6" t="n">
-        <v>5223</v>
+        <v>5828</v>
       </c>
       <c r="D6" t="n">
-        <v>1442</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>146</v>
+        <v>75</v>
       </c>
       <c r="C7" t="n">
-        <v>2276</v>
+        <v>1889</v>
       </c>
       <c r="D7" t="n">
-        <v>601</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>800</v>
+        <v>657</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>252</v>
+        <v>294</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3437</v>
+        <v>254</v>
       </c>
       <c r="C2" t="n">
-        <v>1748</v>
+        <v>3791</v>
       </c>
       <c r="D2" t="n">
-        <v>23263</v>
+        <v>7598</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3439</v>
+        <v>572</v>
       </c>
       <c r="C3" t="n">
-        <v>2867</v>
+        <v>5836</v>
       </c>
       <c r="D3" t="n">
-        <v>17783</v>
+        <v>10689</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3407</v>
+        <v>967</v>
       </c>
       <c r="C4" t="n">
-        <v>6051</v>
+        <v>6148</v>
       </c>
       <c r="D4" t="n">
-        <v>13990</v>
+        <v>9717</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2147</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>8161</v>
+        <v>6982</v>
       </c>
       <c r="D5" t="n">
-        <v>6343</v>
+        <v>5021</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1065</v>
+        <v>303</v>
       </c>
       <c r="C6" t="n">
-        <v>6664</v>
+        <v>5954</v>
       </c>
       <c r="D6" t="n">
-        <v>1944</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>3452</v>
+        <v>2561</v>
       </c>
       <c r="D7" t="n">
-        <v>707</v>
+        <v>593</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>1358</v>
+        <v>745</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>428</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>128</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2346</v>
+        <v>179</v>
       </c>
       <c r="C2" t="n">
-        <v>2059</v>
+        <v>5680</v>
       </c>
       <c r="D2" t="n">
-        <v>16230</v>
+        <v>12503</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3013</v>
+        <v>355</v>
       </c>
       <c r="C3" t="n">
-        <v>2211</v>
+        <v>4112</v>
       </c>
       <c r="D3" t="n">
-        <v>17643</v>
+        <v>9527</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3143</v>
+        <v>682</v>
       </c>
       <c r="C4" t="n">
-        <v>4815</v>
+        <v>5905</v>
       </c>
       <c r="D4" t="n">
-        <v>14172</v>
+        <v>9505</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2384</v>
+        <v>797</v>
       </c>
       <c r="C5" t="n">
-        <v>7555</v>
+        <v>6396</v>
       </c>
       <c r="D5" t="n">
-        <v>7018</v>
+        <v>5724</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1245</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>7392</v>
+        <v>6469</v>
       </c>
       <c r="D6" t="n">
-        <v>2357</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>147</v>
       </c>
       <c r="C7" t="n">
-        <v>4409</v>
+        <v>4222</v>
       </c>
       <c r="D7" t="n">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="C8" t="n">
-        <v>1839</v>
+        <v>1606</v>
       </c>
       <c r="D8" t="n">
-        <v>416</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3632</v>
+        <v>831</v>
       </c>
       <c r="C2" t="n">
-        <v>10992</v>
+        <v>8196</v>
       </c>
       <c r="D2" t="n">
-        <v>29934</v>
+        <v>16576</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2337</v>
+        <v>232</v>
       </c>
       <c r="C3" t="n">
-        <v>1913</v>
+        <v>4263</v>
       </c>
       <c r="D3" t="n">
-        <v>16344</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2718</v>
+        <v>470</v>
       </c>
       <c r="C4" t="n">
-        <v>3614</v>
+        <v>4869</v>
       </c>
       <c r="D4" t="n">
-        <v>14240</v>
+        <v>9219</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2403</v>
+        <v>685</v>
       </c>
       <c r="C5" t="n">
-        <v>6293</v>
+        <v>6022</v>
       </c>
       <c r="D5" t="n">
-        <v>7766</v>
+        <v>6112</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1511</v>
+        <v>569</v>
       </c>
       <c r="C6" t="n">
-        <v>7392</v>
+        <v>6368</v>
       </c>
       <c r="D6" t="n">
-        <v>2908</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>518</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>5561</v>
+        <v>5255</v>
       </c>
       <c r="D7" t="n">
-        <v>968</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>2719</v>
+        <v>2759</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>420</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4761</v>
+        <v>5378</v>
       </c>
       <c r="C2" t="n">
-        <v>2683</v>
+        <v>5508</v>
       </c>
       <c r="D2" t="n">
-        <v>16145</v>
+        <v>12701</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2628</v>
+        <v>721</v>
       </c>
       <c r="C2" t="n">
-        <v>6331</v>
+        <v>10505</v>
       </c>
       <c r="D2" t="n">
-        <v>22270</v>
+        <v>19795</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3161</v>
+        <v>386</v>
       </c>
       <c r="C3" t="n">
-        <v>4115</v>
+        <v>5316</v>
       </c>
       <c r="D3" t="n">
-        <v>18323</v>
+        <v>9621</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3611</v>
+        <v>325</v>
       </c>
       <c r="C4" t="n">
-        <v>5646</v>
+        <v>4447</v>
       </c>
       <c r="D4" t="n">
-        <v>14577</v>
+        <v>8862</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1440</v>
+        <v>550</v>
       </c>
       <c r="C5" t="n">
-        <v>9915</v>
+        <v>5387</v>
       </c>
       <c r="D5" t="n">
-        <v>7016</v>
+        <v>6403</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>478</v>
+        <v>575</v>
       </c>
       <c r="C6" t="n">
-        <v>6826</v>
+        <v>6100</v>
       </c>
       <c r="D6" t="n">
-        <v>2250</v>
+        <v>3272</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>338</v>
       </c>
       <c r="C7" t="n">
-        <v>2664</v>
+        <v>5721</v>
       </c>
       <c r="D7" t="n">
-        <v>566</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>915</v>
+        <v>3760</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>294</v>
+        <v>1634</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>248</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>545</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>91</v>
+        <v>190</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7146</v>
+        <v>4315</v>
       </c>
       <c r="C2" t="n">
-        <v>5167</v>
+        <v>8451</v>
       </c>
       <c r="D2" t="n">
-        <v>19660</v>
+        <v>22491</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2024</v>
+        <v>1776</v>
       </c>
       <c r="C3" t="n">
-        <v>1352</v>
+        <v>2175</v>
       </c>
       <c r="D3" t="n">
-        <v>3351</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5210</v>
+        <v>2664</v>
       </c>
       <c r="C2" t="n">
-        <v>4366</v>
+        <v>4893</v>
       </c>
       <c r="D2" t="n">
-        <v>22147</v>
+        <v>22335</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3760</v>
+        <v>2560</v>
       </c>
       <c r="C3" t="n">
-        <v>3027</v>
+        <v>5125</v>
       </c>
       <c r="D3" t="n">
-        <v>5844</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>913</v>
+        <v>846</v>
       </c>
       <c r="C4" t="n">
-        <v>836</v>
+        <v>1404</v>
       </c>
       <c r="D4" t="n">
-        <v>1856</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>340</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>327</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4669</v>
+        <v>2657</v>
       </c>
       <c r="C2" t="n">
-        <v>4814</v>
+        <v>3372</v>
       </c>
       <c r="D2" t="n">
-        <v>33713</v>
+        <v>19144</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3676</v>
+        <v>2155</v>
       </c>
       <c r="C3" t="n">
-        <v>3252</v>
+        <v>4335</v>
       </c>
       <c r="D3" t="n">
-        <v>8031</v>
+        <v>8086</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1974</v>
+        <v>1494</v>
       </c>
       <c r="C4" t="n">
-        <v>2059</v>
+        <v>3589</v>
       </c>
       <c r="D4" t="n">
-        <v>2565</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="C5" t="n">
-        <v>550</v>
+        <v>891</v>
       </c>
       <c r="D5" t="n">
-        <v>1260</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>261</v>
       </c>
       <c r="D6" t="n">
-        <v>915</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>287</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>250</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>194</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5248</v>
+        <v>2503</v>
       </c>
       <c r="C2" t="n">
-        <v>11348</v>
+        <v>7123</v>
       </c>
       <c r="D2" t="n">
-        <v>33488</v>
+        <v>20666</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3415</v>
+        <v>1980</v>
       </c>
       <c r="C3" t="n">
-        <v>3568</v>
+        <v>3283</v>
       </c>
       <c r="D3" t="n">
-        <v>11369</v>
+        <v>9273</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2380</v>
+        <v>1579</v>
       </c>
       <c r="C4" t="n">
-        <v>2637</v>
+        <v>3944</v>
       </c>
       <c r="D4" t="n">
-        <v>3459</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>999</v>
+        <v>810</v>
       </c>
       <c r="C5" t="n">
-        <v>1335</v>
+        <v>2374</v>
       </c>
       <c r="D5" t="n">
-        <v>1459</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>254</v>
+        <v>233</v>
       </c>
       <c r="C6" t="n">
-        <v>425</v>
+        <v>596</v>
       </c>
       <c r="D6" t="n">
-        <v>961</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>658</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="D8" t="n">
-        <v>482</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>309</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6298</v>
+        <v>3714</v>
       </c>
       <c r="C2" t="n">
-        <v>10577</v>
+        <v>8511</v>
       </c>
       <c r="D2" t="n">
-        <v>27993</v>
+        <v>24895</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3147</v>
+        <v>1855</v>
       </c>
       <c r="C3" t="n">
-        <v>6238</v>
+        <v>4603</v>
       </c>
       <c r="D3" t="n">
-        <v>13105</v>
+        <v>10351</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1811</v>
+        <v>1519</v>
       </c>
       <c r="C4" t="n">
-        <v>2591</v>
+        <v>3500</v>
       </c>
       <c r="D4" t="n">
-        <v>4158</v>
+        <v>4315</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>877</v>
+        <v>1037</v>
       </c>
       <c r="C5" t="n">
-        <v>1480</v>
+        <v>3153</v>
       </c>
       <c r="D5" t="n">
-        <v>1442</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>298</v>
+        <v>452</v>
       </c>
       <c r="C6" t="n">
-        <v>592</v>
+        <v>1494</v>
       </c>
       <c r="D6" t="n">
-        <v>788</v>
+        <v>911</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>248</v>
+        <v>442</v>
       </c>
       <c r="D7" t="n">
-        <v>521</v>
+        <v>611</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>302</v>
       </c>
       <c r="D8" t="n">
-        <v>362</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>345</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4854</v>
+        <v>2675</v>
       </c>
       <c r="C2" t="n">
-        <v>6626</v>
+        <v>12052</v>
       </c>
       <c r="D2" t="n">
-        <v>22286</v>
+        <v>32906</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3930</v>
+        <v>2206</v>
       </c>
       <c r="C3" t="n">
-        <v>7571</v>
+        <v>5709</v>
       </c>
       <c r="D3" t="n">
-        <v>14739</v>
+        <v>11733</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2161</v>
+        <v>1448</v>
       </c>
       <c r="C4" t="n">
-        <v>4777</v>
+        <v>3998</v>
       </c>
       <c r="D4" t="n">
-        <v>5921</v>
+        <v>5185</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1207</v>
+        <v>1112</v>
       </c>
       <c r="C5" t="n">
-        <v>2110</v>
+        <v>3260</v>
       </c>
       <c r="D5" t="n">
-        <v>1945</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>548</v>
+        <v>653</v>
       </c>
       <c r="C6" t="n">
-        <v>1096</v>
+        <v>2260</v>
       </c>
       <c r="D6" t="n">
-        <v>894</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>174</v>
+        <v>251</v>
       </c>
       <c r="C7" t="n">
-        <v>443</v>
+        <v>946</v>
       </c>
       <c r="D7" t="n">
-        <v>568</v>
+        <v>645</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="D8" t="n">
-        <v>387</v>
+        <v>468</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>280</v>
+        <v>353</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>206</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5579</v>
+        <v>2478</v>
       </c>
       <c r="C2" t="n">
-        <v>9906</v>
+        <v>7327</v>
       </c>
       <c r="D2" t="n">
-        <v>34160</v>
+        <v>25760</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3615</v>
+        <v>2774</v>
       </c>
       <c r="C3" t="n">
-        <v>6087</v>
+        <v>9099</v>
       </c>
       <c r="D3" t="n">
-        <v>14885</v>
+        <v>13271</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2631</v>
+        <v>1027</v>
       </c>
       <c r="C4" t="n">
-        <v>6286</v>
+        <v>5662</v>
       </c>
       <c r="D4" t="n">
-        <v>7377</v>
+        <v>4899</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1486</v>
+        <v>603</v>
       </c>
       <c r="C5" t="n">
-        <v>3551</v>
+        <v>2214</v>
       </c>
       <c r="D5" t="n">
-        <v>2649</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>791</v>
+        <v>231</v>
       </c>
       <c r="C6" t="n">
-        <v>1628</v>
+        <v>927</v>
       </c>
       <c r="D6" t="n">
-        <v>1073</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>319</v>
+        <v>99</v>
       </c>
       <c r="C7" t="n">
-        <v>788</v>
+        <v>358</v>
       </c>
       <c r="D7" t="n">
-        <v>614</v>
+        <v>458</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>339</v>
+        <v>282</v>
       </c>
       <c r="D8" t="n">
-        <v>414</v>
+        <v>345</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
         <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>145</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
